--- a/data/trans_bre/P12_1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,05</t>
+          <t>-0,51; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,72</t>
+          <t>8,89; 17,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 7,93</t>
+          <t>-0,21; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,72</t>
+          <t>0,52; 7,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 50,81</t>
+          <t>-3,37; 53,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,73; 161,85</t>
+          <t>61,59; 163,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 63,38</t>
+          <t>-1,32; 63,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 59,12</t>
+          <t>3,13; 57,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,75</t>
+          <t>2,19; 9,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,85</t>
+          <t>3,58; 10,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,17</t>
+          <t>1,72; 7,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 14,63</t>
+          <t>6,15; 14,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 61,19</t>
+          <t>10,61; 61,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,57; 76,59</t>
+          <t>19,51; 73,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,46; 90,61</t>
+          <t>13,69; 86,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,19; 346,63</t>
+          <t>56,9; 346,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,6</t>
+          <t>1,93; 10,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 15,13</t>
+          <t>6,76; 14,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,67</t>
+          <t>2,43; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 50,34</t>
+          <t>1,48; 55,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 69,31</t>
+          <t>9,18; 70,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,48; 114,14</t>
+          <t>38,54; 112,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,32; 110,48</t>
+          <t>19,89; 108,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 383,03</t>
+          <t>9,09; 492,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,6</t>
+          <t>2,3; 9,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,16</t>
+          <t>6,6; 14,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,53</t>
+          <t>1,74; 8,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,37</t>
+          <t>1,41; 9,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 61,78</t>
+          <t>12,16; 63,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,15; 86,27</t>
+          <t>32,78; 88,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 79,53</t>
+          <t>12,06; 77,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 71,96</t>
+          <t>9,47; 71,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,31</t>
+          <t>3,65; 7,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,07</t>
+          <t>8,3; 12,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,67</t>
+          <t>3,23; 6,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,63</t>
+          <t>5,45; 26,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 45,95</t>
+          <t>20,35; 46,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,25; 80,52</t>
+          <t>48,74; 79,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,82; 62,09</t>
+          <t>25,75; 61,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,47; 225,35</t>
+          <t>40,26; 231,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,26</t>
+          <t>-0,75; 7,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,55</t>
+          <t>9,45; 17,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 7,75</t>
+          <t>-0,09; 8,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,29</t>
+          <t>-0,05; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 53,97</t>
+          <t>-4,23; 53,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,59; 163,64</t>
+          <t>63,77; 164,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 63,19</t>
+          <t>-0,7; 64,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 57,09</t>
+          <t>-0,61; 54,69</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>115,36%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,87</t>
+          <t>2,27; 9,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 10,63</t>
+          <t>3,68; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,78</t>
+          <t>2,0; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,24</t>
+          <t>4,55; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 61,56</t>
+          <t>11,52; 62,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,51; 73,1</t>
+          <t>20,01; 72,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 86,8</t>
+          <t>16,0; 85,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,9; 346,17</t>
+          <t>36,99; 112,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,06</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>143,28%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,3</t>
+          <t>1,13; 10,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,66</t>
+          <t>6,59; 15,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,8</t>
+          <t>2,51; 9,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 55,69</t>
+          <t>0,8; 8,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 70,19</t>
+          <t>5,88; 68,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,54; 112,9</t>
+          <t>37,51; 120,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,89; 108,99</t>
+          <t>20,14; 109,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 492,34</t>
+          <t>4,16; 76,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 9,64</t>
+          <t>2,24; 9,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,34</t>
+          <t>6,32; 14,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,34</t>
+          <t>1,79; 8,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,31</t>
+          <t>4,2; 10,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 63,3</t>
+          <t>11,86; 61,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 88,12</t>
+          <t>29,99; 85,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 77,27</t>
+          <t>12,41; 77,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 71,22</t>
+          <t>25,51; 79,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,42</t>
+          <t>3,38; 7,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,04</t>
+          <t>8,25; 12,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,68</t>
+          <t>3,24; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 26,46</t>
+          <t>4,48; 7,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,35; 46,14</t>
+          <t>19,08; 46,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,74; 79,47</t>
+          <t>49,0; 82,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 61,27</t>
+          <t>25,82; 61,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,26; 231,53</t>
+          <t>31,34; 62,27</t>
         </is>
       </c>
     </row>
